--- a/测试用例/哈尔滨冰城医疗美容医院/处理后表格/7月__冰城医美账单.xlsx
+++ b/测试用例/哈尔滨冰城医疗美容医院/处理后表格/7月__冰城医美账单.xlsx
@@ -437,27 +437,7 @@
     </row>
     <row r="5"/>
     <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="I8" t="inlineStr">
         <is>
@@ -3445,10 +3425,10 @@
         <v>5</v>
       </c>
       <c r="O81" t="n">
-        <v>33.5</v>
+        <v>30.5</v>
       </c>
       <c r="P81" t="n">
-        <v>33.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="82">
@@ -4004,10 +3984,10 @@
         <v>10</v>
       </c>
       <c r="O94" t="n">
-        <v>33.5</v>
+        <v>30.5</v>
       </c>
       <c r="P94" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95">
@@ -4569,32 +4549,8 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-    </row>
+    <row r="108"/>
+    <row r="109"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
